--- a/编程/数据集/各阶段新生招生数.xlsx
+++ b/编程/数据集/各阶段新生招生数.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\数模校赛\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\数模校赛\Mm\编程\数据集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40075178-CC71-445A-95C4-C136652D786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96DBD65-80B1-4165-A245-83A2DF3C7BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4584" yWindow="3984" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
